--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_ESG.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_ESG.xlsx
@@ -13,8 +13,8 @@
     <sheet name="duos_trios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -458,7 +458,11 @@
           <t>team_name</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,60 +472,96 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>base_lineup</t>
+          <t>primary_scorer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F. Ferreira | J. Bailey | M. Pombo | P. Carvalhal | Y. Antonio (14.9 min)</t>
+          <t>J. Bailey (19 ppg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>best_lineup</t>
+          <t>most_used_player</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F. Ferreira | J. Bailey | M. Pombo | P. Carvalhal | Y. Antonio (10.7 net)</t>
+          <t>J. Bailey (36.7 mpg)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>best_duo</t>
+          <t>best_3pt_pct</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Bailey | P. Carvalhal (-21.7 net)</t>
+          <t>F. Ferreira (50.0%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>base_lineup</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D. Carr | F. Ferreira | J. Bailey | O. Onyeka | P. Carvalhal (15.3 min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>best_lineup</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>F. Ferreira | J. Bailey | M. Pombo | P. Carvalhal | Y. Antonio (10.7 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>best_duo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Bailey | P. Carvalhal (-25.8 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>best_trio</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>F. Ferreira | J. Bailey | P. Carvalhal (-35.4 net)</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>F. Ferreira | J. Bailey | P. Carvalhal (-34.8 net)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B8"/>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -532,28 +572,461 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="38" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>playing_position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games_started</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes_total</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>bpg</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>tp_pct</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ft_pct</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>efg_pct</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ts_pct</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>plus_minus_pg</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>on_off_net_diff_per40</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>role_tag</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>J. Bailey</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>19</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>33.8%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>42.4%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>-26</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-32.8</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P. Carvalhal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>34.6%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>81.8%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>42.3%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>50.3%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>43.2%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>-23</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-18.6</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>high-minutes, shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Bertino</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-23.5</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:U5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -656,7 +1129,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>F. Ferreira | J. Bailey | M. Pombo | P. Carvalhal | Y. Antonio</t>
+          <t>D. Carr | F. Ferreira | J. Bailey | O. Onyeka | P. Carvalhal</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -666,25 +1139,25 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="G2" t="n">
-        <v>64.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>53.5</v>
+        <v>102.1</v>
       </c>
       <c r="I2" t="n">
-        <v>10.7</v>
+        <v>-36.6</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -722,13 +1195,13 @@
         <v>10.7</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -766,13 +1239,13 @@
         <v>10.7</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -810,13 +1283,13 @@
         <v>-76</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -837,7 +1310,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -920,22 +1393,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>38.6</v>
+        <v>68.2</v>
       </c>
       <c r="H2" t="n">
-        <v>63.1</v>
+        <v>62.2</v>
       </c>
       <c r="I2" t="n">
-        <v>84.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="J2" t="n">
-        <v>-21.7</v>
+        <v>-25.8</v>
       </c>
     </row>
     <row r="3">
@@ -960,22 +1433,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>38.6</v>
+        <v>68.2</v>
       </c>
       <c r="H3" t="n">
-        <v>63.1</v>
+        <v>62.2</v>
       </c>
       <c r="I3" t="n">
-        <v>84.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.7</v>
+        <v>-25.8</v>
       </c>
     </row>
     <row r="4">
@@ -1000,22 +1473,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>31.6</v>
+        <v>51</v>
       </c>
       <c r="H4" t="n">
-        <v>50.7</v>
+        <v>56.5</v>
       </c>
       <c r="I4" t="n">
-        <v>81.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>-30.4</v>
+        <v>-30.6</v>
       </c>
     </row>
     <row r="5">
@@ -1040,22 +1513,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>30.5</v>
+        <v>46</v>
       </c>
       <c r="H5" t="n">
-        <v>48.4</v>
+        <v>54.8</v>
       </c>
       <c r="I5" t="n">
-        <v>83.8</v>
+        <v>89.5</v>
       </c>
       <c r="J5" t="n">
-        <v>-35.4</v>
+        <v>-34.8</v>
       </c>
     </row>
     <row r="6">
@@ -1076,26 +1549,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>J. Bailey | M. Pombo | P. Carvalhal</t>
+          <t>F. Ferreira | P. Carvalhal | Y. Antonio</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>25.7</v>
+        <v>31.4</v>
       </c>
       <c r="H6" t="n">
-        <v>77.90000000000001</v>
+        <v>53.5</v>
       </c>
       <c r="I6" t="n">
-        <v>71.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>6.2</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="7">
@@ -1116,26 +1589,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>J. Bailey | M. Pombo | P. Carvalhal</t>
+          <t>F. Ferreira | P. Carvalhal | Y. Antonio</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>25.7</v>
+        <v>31.4</v>
       </c>
       <c r="H7" t="n">
-        <v>77.90000000000001</v>
+        <v>53.5</v>
       </c>
       <c r="I7" t="n">
-        <v>71.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>6.2</v>
+        <v>-28</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_ESG.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_ESG.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Bailey (19 ppg)</t>
+          <t>J. Bailey (24 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Bailey (36.7 mpg)</t>
+          <t>J. Bailey (37.5 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F. Ferreira (50.0%)</t>
+          <t>F. Ferreira (66.7%)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D. Carr | F. Ferreira | J. Bailey | O. Onyeka | P. Carvalhal (15.3 min)</t>
+          <t>D. Carr | F. Ferreira | J. Bailey | O. Onyeka | P. Carvalhal (36.8 min)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Bailey | P. Carvalhal (-25.8 net)</t>
+          <t>J. Bailey | P. Carvalhal (-16.2 net)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F. Ferreira | J. Bailey | P. Carvalhal (-34.8 net)</t>
+          <t>F. Ferreira | J. Bailey | P. Carvalhal (-22.0 net)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="38" customWidth="1" min="21" max="21"/>
+    <col width="41" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -718,19 +718,19 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>73.40000000000001</v>
+        <v>112.5</v>
       </c>
       <c r="G2" t="n">
-        <v>36.7</v>
+        <v>37.5</v>
       </c>
       <c r="H2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I2" t="n">
         <v>6</v>
@@ -742,41 +742,41 @@
         <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>-26</v>
+        <v>-19</v>
       </c>
       <c r="T2" t="n">
-        <v>-32.8</v>
+        <v>-18.5</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -801,28 +801,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>73.40000000000001</v>
+        <v>111.9</v>
       </c>
       <c r="G3" t="n">
-        <v>36.7</v>
+        <v>37.3</v>
       </c>
       <c r="H3" t="n">
-        <v>15.5</v>
+        <v>16.3</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
         <v>2</v>
@@ -832,38 +832,38 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>-20.5</v>
+        <v>-13</v>
       </c>
       <c r="T3" t="n">
-        <v>6.9</v>
+        <v>29.4</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, impact</t>
+          <t>high-minutes, primary-scorer, shooter</t>
         </is>
       </c>
     </row>
@@ -884,65 +884,65 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>57.5</v>
+        <v>81.5</v>
       </c>
       <c r="G4" t="n">
-        <v>28.8</v>
+        <v>27.2</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>-23</v>
+        <v>-15</v>
       </c>
       <c r="T4" t="n">
-        <v>-18.6</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -966,67 +966,387 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>56.8%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>59.0%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="T5" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>38.1%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>40.5%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>45.3%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>-13</v>
+      </c>
+      <c r="T6" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>high-minutes, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J. Bertino</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="F7" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-25.6</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Y. Antonio</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="K8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-23.5</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="M8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>33.8%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>rotation</t>
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M. Pombo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>7.3%</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U5"/>
+  <autoFilter ref="A1:U9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1037,7 +1357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1133,31 +1453,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>15.3</v>
+        <v>36.8</v>
       </c>
       <c r="G2" t="n">
-        <v>65.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="H2" t="n">
-        <v>102.1</v>
+        <v>97.7</v>
       </c>
       <c r="I2" t="n">
-        <v>-36.6</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -1198,10 +1518,10 @@
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -1242,10 +1562,10 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -1261,39 +1581,83 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>F. Ferreira | J. Bailey | J. Bertino | P. Carvalhal | Y. Antonio</t>
+          <t>D. Carr | J. Bailey | J. Bertino | O. Onyeka | P. Carvalhal</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>12.1</v>
+        <v>14.4</v>
       </c>
       <c r="G5" t="n">
-        <v>36.4</v>
+        <v>80.5</v>
       </c>
       <c r="H5" t="n">
-        <v>112.4</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-76</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>15</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rotation lineup</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>F. Ferreira | J. Bailey | J. Bertino | P. Carvalhal | Y. Antonio</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-76</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>22</v>
+      </c>
+      <c r="L6" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L5"/>
+  <autoFilter ref="A1:L6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1310,7 +1674,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1393,22 +1757,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>68.2</v>
+        <v>105.9</v>
       </c>
       <c r="H2" t="n">
-        <v>62.2</v>
+        <v>73.3</v>
       </c>
       <c r="I2" t="n">
-        <v>88</v>
+        <v>89.5</v>
       </c>
       <c r="J2" t="n">
-        <v>-25.8</v>
+        <v>-16.2</v>
       </c>
     </row>
     <row r="3">
@@ -1429,26 +1793,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>J. Bailey | P. Carvalhal</t>
+          <t>J. Bailey | O. Onyeka</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>68.2</v>
+        <v>66.2</v>
       </c>
       <c r="H3" t="n">
-        <v>62.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>88</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-25.8</v>
+        <v>-10.3</v>
       </c>
     </row>
     <row r="4">
@@ -1469,26 +1833,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>F. Ferreira | P. Carvalhal</t>
+          <t>J. Bailey | O. Onyeka</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>51</v>
+        <v>66.2</v>
       </c>
       <c r="H4" t="n">
-        <v>56.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>87.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>-30.6</v>
+        <v>-10.3</v>
       </c>
     </row>
     <row r="5">
@@ -1513,22 +1877,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>46</v>
+        <v>69.2</v>
       </c>
       <c r="H5" t="n">
-        <v>54.8</v>
+        <v>68.8</v>
       </c>
       <c r="I5" t="n">
-        <v>89.5</v>
+        <v>90.8</v>
       </c>
       <c r="J5" t="n">
-        <v>-34.8</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="6">
@@ -1549,26 +1913,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>F. Ferreira | P. Carvalhal | Y. Antonio</t>
+          <t>J. Bailey | O. Onyeka | P. Carvalhal</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>31.4</v>
+        <v>59.5</v>
       </c>
       <c r="H6" t="n">
-        <v>53.5</v>
+        <v>83.3</v>
       </c>
       <c r="I6" t="n">
-        <v>81.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="J6" t="n">
-        <v>-28</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="7">
@@ -1589,26 +1953,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>F. Ferreira | P. Carvalhal | Y. Antonio</t>
+          <t>D. Carr | O. Onyeka | P. Carvalhal</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>31.4</v>
+        <v>57.8</v>
       </c>
       <c r="H7" t="n">
-        <v>53.5</v>
+        <v>82.3</v>
       </c>
       <c r="I7" t="n">
-        <v>81.59999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-28</v>
+        <v>-5.5</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_ESG.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_ESG.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Bailey (24 ppg)</t>
+          <t>J. Bailey (21.5 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Bailey (37.5 mpg)</t>
+          <t>J. Bailey (37.0 mpg)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Bailey | P. Carvalhal (-16.2 net)</t>
+          <t>J. Bailey | P. Carvalhal (-20.2 net)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F. Ferreira | J. Bailey | P. Carvalhal (-22.0 net)</t>
+          <t>D. Carr | J. Bailey | P. Carvalhal (-21.8 net)</t>
         </is>
       </c>
     </row>
@@ -718,65 +718,65 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>112.5</v>
+        <v>147.8</v>
       </c>
       <c r="G2" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="H2" t="n">
-        <v>24</v>
+        <v>21.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>-19</v>
+        <v>-19.5</v>
       </c>
       <c r="T2" t="n">
-        <v>-18.5</v>
+        <v>-9.9</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -797,47 +797,47 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>111.9</v>
+        <v>139.3</v>
       </c>
       <c r="G3" t="n">
-        <v>37.3</v>
+        <v>34.8</v>
       </c>
       <c r="H3" t="n">
-        <v>16.3</v>
+        <v>12.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -847,23 +847,23 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>-13</v>
+        <v>-14.8</v>
       </c>
       <c r="T3" t="n">
-        <v>29.4</v>
+        <v>-4.1</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, shooter</t>
+          <t>high-minutes, primary-scorer</t>
         </is>
       </c>
     </row>
@@ -875,14 +875,10 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+          <t>D. Carr</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
         <v>3</v>
       </c>
@@ -890,63 +886,63 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>81.5</v>
+        <v>105.7</v>
       </c>
       <c r="G4" t="n">
-        <v>27.2</v>
+        <v>35.2</v>
       </c>
       <c r="H4" t="n">
-        <v>8.300000000000001</v>
+        <v>17.3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>13.3</v>
       </c>
       <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
         <v>2.3</v>
       </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
       <c r="L4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M4" t="n">
         <v>0.3</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>-15</v>
+        <v>-16.7</v>
       </c>
       <c r="T4" t="n">
-        <v>-8.699999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes, shooter</t>
+          <t>high-minutes, primary-scorer, efficient</t>
         </is>
       </c>
     </row>
@@ -958,74 +954,78 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Carr</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>71.59999999999999</v>
+        <v>100.7</v>
       </c>
       <c r="G5" t="n">
-        <v>35.8</v>
+        <v>25.2</v>
       </c>
       <c r="H5" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>2.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="K5" t="n">
         <v>2.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>-10</v>
+        <v>-13.2</v>
       </c>
       <c r="T5" t="n">
-        <v>40.6</v>
+        <v>4.1</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, efficient</t>
+          <t>high-minutes, shooter</t>
         </is>
       </c>
     </row>
@@ -1042,22 +1042,22 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>68.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>34.5</v>
+        <v>31</v>
       </c>
       <c r="H6" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="I6" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -1066,41 +1066,41 @@
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>-13</v>
+        <v>-8</v>
       </c>
       <c r="T6" t="n">
-        <v>19.2</v>
+        <v>41.1</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1116,66 +1116,70 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>62</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.3</v>
-      </c>
       <c r="K7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>-12.3</v>
+        <v>-10</v>
       </c>
       <c r="T7" t="n">
-        <v>-25.6</v>
+        <v>-20.6</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1191,70 +1195,66 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>J. Bertino</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="F8" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.3</v>
-      </c>
       <c r="J8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.7</v>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-10.8</v>
       </c>
       <c r="T8" t="n">
-        <v>-19.9</v>
+        <v>-21.5</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1279,25 +1279,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="G9" t="n">
-        <v>14.4</v>
+        <v>11.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>-3.7</v>
+        <v>-3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>14.1</v>
+        <v>12</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1474,10 +1474,10 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -1518,7 +1518,7 @@
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
         <v>11</v>
@@ -1562,7 +1562,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
         <v>11</v>
@@ -1606,10 +1606,10 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>F. Ferreira | J. Bailey | J. Bertino | P. Carvalhal | Y. Antonio</t>
+          <t>D. Carr | J. Bailey | O. Onyeka | P. Carvalhal | Z. James</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1635,29 +1635,73 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>12.1</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>36.4</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>112.4</v>
+        <v>116.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-76</v>
+        <v>-30.7</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L6" t="n">
-        <v>21</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rotation lineup</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>F. Ferreira | J. Bailey | J. Bertino | P. Carvalhal | Y. Antonio</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-76</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L7" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L6"/>
+  <autoFilter ref="A1:L7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1757,22 +1801,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>105.9</v>
+        <v>128.5</v>
       </c>
       <c r="H2" t="n">
-        <v>73.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>89.5</v>
+        <v>94.3</v>
       </c>
       <c r="J2" t="n">
-        <v>-16.2</v>
+        <v>-20.2</v>
       </c>
     </row>
     <row r="3">
@@ -1793,26 +1837,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>J. Bailey | O. Onyeka</t>
+          <t>F. Ferreira | J. Bailey</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>66.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>79.09999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>89.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-10.3</v>
+        <v>-19.3</v>
       </c>
     </row>
     <row r="4">
@@ -1833,26 +1877,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>J. Bailey | O. Onyeka</t>
+          <t>F. Ferreira | Y. Antonio</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>66.2</v>
+        <v>45.8</v>
       </c>
       <c r="H4" t="n">
-        <v>79.09999999999999</v>
+        <v>55</v>
       </c>
       <c r="I4" t="n">
-        <v>89.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="J4" t="n">
-        <v>-10.3</v>
+        <v>-27.1</v>
       </c>
     </row>
     <row r="5">
@@ -1873,26 +1917,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>F. Ferreira | J. Bailey | P. Carvalhal</t>
+          <t>D. Carr | J. Bailey | P. Carvalhal</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>69.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>68.8</v>
+        <v>77.3</v>
       </c>
       <c r="I5" t="n">
-        <v>90.8</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>-22</v>
+        <v>-21.8</v>
       </c>
     </row>
     <row r="6">
@@ -1913,26 +1957,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>J. Bailey | O. Onyeka | P. Carvalhal</t>
+          <t>F. Ferreira | J. Bailey | P. Carvalhal</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>59.5</v>
+        <v>71</v>
       </c>
       <c r="H6" t="n">
-        <v>83.3</v>
+        <v>69.3</v>
       </c>
       <c r="I6" t="n">
-        <v>88.7</v>
+        <v>91.2</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.4</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="7">
@@ -1953,26 +1997,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>D. Carr | O. Onyeka | P. Carvalhal</t>
+          <t>F. Ferreira | J. Bailey | Y. Antonio</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>57.8</v>
+        <v>38.2</v>
       </c>
       <c r="H7" t="n">
-        <v>82.3</v>
+        <v>50.2</v>
       </c>
       <c r="I7" t="n">
-        <v>87.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-5.5</v>
+        <v>-31.4</v>
       </c>
     </row>
   </sheetData>
